--- a/Los_Angeles_Lakers_2025-26_stats.xlsx
+++ b/Los_Angeles_Lakers_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,75 +449,80 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Adou Thiero</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Jarred Vanderbilt</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Dalton Knecht</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Deandre Ayton</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Gabe Vincent</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Bronny James</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Christian Koloko</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Jaxson Hayes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jake LaRavia</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Maxi Kleber</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Austin Reaves</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Nick Smith Jr.</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Rui Hachimura</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Chris Mañon</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Marcus Smart</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Luka Dončić</t>
         </is>
@@ -541,42 +546,45 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
         <v>4</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>5</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>26</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>9</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>9</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>43</v>
       </c>
     </row>
@@ -592,20 +600,20 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>15</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>5</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
@@ -613,27 +621,30 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>6</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>25</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>23</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>49</v>
       </c>
     </row>
@@ -649,20 +660,20 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
         <v>9</v>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
       <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
         <v>22</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
@@ -670,27 +681,30 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>11</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>51</v>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>18</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>11</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -706,16 +720,16 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
         <v>14</v>
-      </c>
-      <c r="D5" t="n">
-        <v>16</v>
       </c>
       <c r="E5" t="n">
         <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -727,27 +741,30 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>3</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>41</v>
       </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
       <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
         <v>16</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -763,17 +780,17 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
         <v>3</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>15</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>17</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
@@ -781,30 +798,33 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
         <v>27</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>28</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>7</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>17</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -820,17 +840,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
         <v>5</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>9</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
@@ -838,30 +858,33 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
         <v>13</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>21</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>9</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>12</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>44</v>
       </c>
     </row>
@@ -877,48 +900,51 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
         <v>4</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>15</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>25</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>26</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>15</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>11</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>29</v>
       </c>
     </row>
@@ -934,48 +960,51 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
         <v>4</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>8</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>29</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>5</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>4</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>11</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>25</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>28</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>9</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -991,48 +1020,51 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
         <v>5</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>3</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>22</v>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>8</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
         <v>15</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>17</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>35</v>
       </c>
     </row>
@@ -1048,48 +1080,51 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
         <v>12</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>14</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>11</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>9</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
       <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>13</v>
       </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>3</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>8</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>5</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>22</v>
       </c>
     </row>
@@ -1108,14 +1143,14 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
         <v>3</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>14</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
@@ -1123,30 +1158,33 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
         <v>6</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>24</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>21</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>13</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>38</v>
       </c>
     </row>
@@ -1162,17 +1200,17 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
         <v>6</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>16</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>6</v>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
@@ -1180,31 +1218,154 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>3</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>13</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>13</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>9</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>31</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>14</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>13</v>
+      </c>
+      <c r="R14" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>20</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>25</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1234,75 +1395,80 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Adou Thiero</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Jarred Vanderbilt</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Dalton Knecht</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Deandre Ayton</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Gabe Vincent</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Bronny James</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Christian Koloko</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Jaxson Hayes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jake LaRavia</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Maxi Kleber</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Austin Reaves</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Nick Smith Jr.</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Rui Hachimura</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Chris Mañon</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Marcus Smart</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Luka Dončić</t>
         </is>
@@ -1329,39 +1495,42 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>9</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1386,11 +1555,11 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>5</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
@@ -1398,17 +1567,17 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>11</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
@@ -1416,9 +1585,12 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1434,19 +1606,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1455,27 +1627,30 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>5</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>9</v>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>5</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1491,48 +1666,51 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>5</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1548,17 +1726,17 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
         <v>4</v>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
       <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
@@ -1566,30 +1744,33 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>16</v>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
       <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
         <v>4</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1605,13 +1786,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1623,30 +1804,33 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>5</v>
       </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>4</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>4</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1674,36 +1858,39 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
         <v>3</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>11</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>4</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1719,48 +1906,51 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>6</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>6</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>6</v>
       </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>5</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1776,13 +1966,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1794,13 +1984,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1815,9 +2005,12 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>5</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1833,48 +2026,51 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1890,10 +2086,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1911,27 +2107,30 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>3</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>7</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>6</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1947,49 +2146,172 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>3</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2003,7 +2325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2019,75 +2341,80 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Adou Thiero</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Jarred Vanderbilt</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Dalton Knecht</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Deandre Ayton</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Gabe Vincent</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Bronny James</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Christian Koloko</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Jaxson Hayes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jake LaRavia</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Maxi Kleber</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Austin Reaves</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Nick Smith Jr.</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Rui Hachimura</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Chris Mañon</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Marcus Smart</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Luka Dončić</t>
         </is>
@@ -2105,17 +2432,17 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
@@ -2123,30 +2450,33 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
         <v>6</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>3</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>5</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>4</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2162,19 +2492,19 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
         <v>7</v>
       </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
       <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
         <v>8</v>
       </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -2189,21 +2519,24 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>7</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2219,19 +2552,19 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
       <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
         <v>15</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -2240,27 +2573,30 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>6</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>11</v>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
       <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2276,48 +2612,51 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
         <v>8</v>
       </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
       <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
         <v>8</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>6</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>4</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>6</v>
       </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2333,17 +2672,17 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
         <v>12</v>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
       <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>10</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
@@ -2351,30 +2690,33 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
         <v>8</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
         <v>5</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2390,13 +2732,13 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
         <v>4</v>
       </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2408,30 +2750,33 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>7</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>5</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>4</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>3</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2447,11 +2792,11 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
         <v>4</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
@@ -2465,30 +2810,33 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>5</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>8</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>4</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>6</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2504,48 +2852,51 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
       </c>
       <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
         <v>10</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>3</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>5</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
         <v>4</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2564,29 +2915,29 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
         <v>10</v>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>4</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>6</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
@@ -2594,15 +2945,18 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>5</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2618,48 +2972,51 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
         <v>18</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>4</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>5</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>5</v>
       </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2675,17 +3032,17 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
         <v>5</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>6</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
@@ -2693,30 +3050,33 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>5</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2732,49 +3092,172 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
         <v>9</v>
       </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
       <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
         <v>5</v>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
         <v>4</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>5</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>5</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2788,7 +3271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2804,75 +3287,80 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Adou Thiero</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Jarred Vanderbilt</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Dalton Knecht</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Deandre Ayton</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Gabe Vincent</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Bronny James</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Christian Koloko</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Jaxson Hayes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jake LaRavia</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Maxi Kleber</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Austin Reaves</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Nick Smith Jr.</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Rui Hachimura</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Chris Mañon</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Marcus Smart</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Luka Dončić</t>
         </is>
@@ -2899,10 +3387,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -2911,27 +3399,30 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2956,10 +3447,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -2968,27 +3459,30 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3025,17 +3519,17 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>6</v>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
@@ -3046,6 +3540,9 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3064,10 +3561,10 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -3088,21 +3585,24 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>3</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3121,10 +3621,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3139,27 +3639,30 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>5</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3178,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3196,27 +3699,30 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3235,10 +3741,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -3250,30 +3756,33 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>4</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3301,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3319,18 +3828,21 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>5</v>
       </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3346,13 +3858,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -3367,10 +3879,10 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -3379,15 +3891,18 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3403,48 +3918,51 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3463,10 +3981,10 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -3487,21 +4005,24 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3517,14 +4038,14 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
         <v>4</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
@@ -3538,28 +4059,151 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3573,7 +4217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3595,7 +4239,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34.875</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="3">
@@ -3605,27 +4249,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28.33333333333333</v>
+        <v>28.27272727272727</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>16.23076923076923</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.54545454545454</v>
+        <v>15.84615384615385</v>
       </c>
     </row>
     <row r="6">
@@ -3635,7 +4279,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.08333333333333</v>
+        <v>10.21428571428571</v>
       </c>
     </row>
     <row r="7">
@@ -3645,67 +4289,67 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.9</v>
+        <v>10.18181818181818</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nick Smith Jr.</t>
+          <t>Dalton Knecht</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.8</v>
+        <v>7.615384615384615</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dalton Knecht</t>
+          <t>Nick Smith Jr.</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.727272727272728</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jarred Vanderbilt</t>
+          <t>Jaxson Hayes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.083333333333333</v>
+        <v>5.090909090909091</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jaxson Hayes</t>
+          <t>Jarred Vanderbilt</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.888888888888889</v>
+        <v>4.571428571428571</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gabe Vincent</t>
+          <t>Adou Thiero</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.666666666666667</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bronny James</t>
+          <t>Gabe Vincent</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.25</v>
+        <v>3.666666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -3715,26 +4359,36 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Christian Koloko</t>
+          <t>Bronny James</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Christian Koloko</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Chris Mañon</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3749,7 +4403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3771,7 +4425,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.875</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3">
@@ -3781,7 +4435,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.333333333333334</v>
+        <v>8.181818181818182</v>
       </c>
     </row>
     <row r="4">
@@ -3791,7 +4445,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.2</v>
+        <v>3.363636363636364</v>
       </c>
     </row>
     <row r="5">
@@ -3801,27 +4455,27 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.666666666666667</v>
+        <v>2.357142857142857</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nick Smith Jr.</t>
+          <t>Gabe Vincent</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.4</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gabe Vincent</t>
+          <t>Nick Smith Jr.</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.333333333333333</v>
+        <v>2.166666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -3831,7 +4485,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.875</v>
+        <v>1.777777777777778</v>
       </c>
     </row>
     <row r="9">
@@ -3841,13 +4495,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.583333333333333</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Maxi Kleber</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -3857,47 +4511,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jaxson Hayes</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.222222222222222</v>
+        <v>1.230769230769231</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Jaxson Hayes</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9090909090909091</v>
+        <v>1.181818181818182</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dalton Knecht</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.9230769230769231</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Maxi Kleber</t>
+          <t>Dalton Knecht</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5</v>
+        <v>0.6153846153846154</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Christian Koloko</t>
+          <t>Adou Thiero</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -3907,10 +4561,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Christian Koloko</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Chris Mañon</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3925,7 +4589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3947,7 +4611,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.125</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3">
@@ -3957,7 +4621,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.545454545454546</v>
+        <v>8.384615384615385</v>
       </c>
     </row>
     <row r="4">
@@ -3967,7 +4631,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.25</v>
+        <v>5.571428571428571</v>
       </c>
     </row>
     <row r="5">
@@ -3977,7 +4641,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.111111111111111</v>
+        <v>5.090909090909091</v>
       </c>
     </row>
     <row r="6">
@@ -3997,7 +4661,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.111111111111111</v>
+        <v>4.181818181818182</v>
       </c>
     </row>
     <row r="8">
@@ -4007,47 +4671,47 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.75</v>
+        <v>3.769230769230769</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Maxi Kleber</t>
+          <t>Dalton Knecht</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2.384615384615385</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dalton Knecht</t>
+          <t>Marcus Smart</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.181818181818182</v>
+        <v>2.363636363636364</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Maxi Kleber</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1</v>
+        <v>2.333333333333333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nick Smith Jr.</t>
+          <t>Adou Thiero</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -4073,7 +4737,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Chris Mañon</t>
+          <t>Nick Smith Jr.</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -4083,10 +4747,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Chris Mañon</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Christian Koloko</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B17" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4101,7 +4775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4123,7 +4797,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="3">
@@ -4133,7 +4807,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.555555555555555</v>
+        <v>2.727272727272727</v>
       </c>
     </row>
     <row r="4">
@@ -4153,37 +4827,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.4</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jake LaRavia</t>
+          <t>Dalton Knecht</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.25</v>
+        <v>1.153846153846154</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dalton Knecht</t>
+          <t>Marcus Smart</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.181818181818182</v>
+        <v>1.090909090909091</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Jake LaRavia</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.1</v>
+        <v>1.071428571428571</v>
       </c>
     </row>
     <row r="9">
@@ -4203,7 +4877,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="11">
@@ -4213,7 +4887,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.25</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="12">
@@ -4223,7 +4897,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.25</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="13">
@@ -4233,13 +4907,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Adou Thiero</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -4249,7 +4923,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Christian Koloko</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -4259,10 +4933,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Christian Koloko</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Chris Mañon</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4277,7 +4961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4559,6 +5243,48 @@
         <v>213</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>118</v>
+      </c>
+      <c r="D14" t="n">
+        <v>104</v>
+      </c>
+      <c r="E14" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>119</v>
+      </c>
+      <c r="D15" t="n">
+        <v>95</v>
+      </c>
+      <c r="E15" t="n">
+        <v>214</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
